--- a/output/reports/cv_experiment_RandomForest_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>28.96171975135803</v>
+        <v>2.144138813018799</v>
       </c>
       <c r="E2" t="n">
-        <v>0.884370648297461</v>
+        <v>0.9951175357102523</v>
       </c>
       <c r="F2" t="n">
-        <v>0.899417278946035</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8986830586723202</v>
+        <v>0.986933650093331</v>
       </c>
       <c r="H2" t="n">
-        <v>0.961681313514882</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>50.91848659515381</v>
+        <v>1.117149114608765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8897925336193475</v>
+        <v>0.9918502377727062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8989105649860654</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.898207607994842</v>
+        <v>0.986933650093331</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9609949523912853</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>28.96171975135803</v>
+        <v>2.144138813018799</v>
       </c>
       <c r="E2" t="n">
-        <v>0.884370648297461</v>
+        <v>0.9951175357102523</v>
       </c>
       <c r="F2" t="n">
-        <v>0.899417278946035</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8986830586723202</v>
+        <v>0.986933650093331</v>
       </c>
       <c r="H2" t="n">
-        <v>0.961681313514882</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>50.91848659515381</v>
+        <v>1.117149114608765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8897925336193475</v>
+        <v>0.9918502377727062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8989105649860654</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.898207607994842</v>
+        <v>0.986933650093331</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9609949523912853</v>
+        <v>0.9994909214322077</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.144138813018799</v>
+        <v>60.56224012374878</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9951175357102523</v>
+        <v>0.6241691152393311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.7627118644067796</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986933650093331</v>
+        <v>0.7354928414695082</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9994909214322077</v>
+        <v>0.9012496409077851</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
+          <t>{'max_depth': 10, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 5, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.117149114608765</v>
+        <v>107.1575047969818</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918502377727062</v>
+        <v>0.665464727118389</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.7754237288135594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986933650093331</v>
+        <v>0.7492025518341308</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9994909214322077</v>
+        <v>0.9101641051422005</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
+          <t>{'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.144138813018799</v>
+        <v>60.56224012374878</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9951175357102523</v>
+        <v>0.6241691152393311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.7627118644067796</v>
       </c>
       <c r="G2" t="n">
-        <v>0.986933650093331</v>
+        <v>0.7354928414695082</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9994909214322077</v>
+        <v>0.9012496409077851</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
+          <t>{'max_depth': 10, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 5, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.117149114608765</v>
+        <v>107.1575047969818</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918502377727062</v>
+        <v>0.665464727118389</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.7754237288135594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.986933650093331</v>
+        <v>0.7492025518341308</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9994909214322077</v>
+        <v>0.9101641051422005</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 6}</t>
+          <t>{'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
